--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/143.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/143.xlsx
@@ -426,13 +426,13 @@
         <v>-13.82418473858437</v>
       </c>
       <c r="E2">
-        <v>-11.26391548510849</v>
+        <v>-10.43331183956961</v>
       </c>
       <c r="F2">
-        <v>-3.35911295029555</v>
+        <v>-3.760634662154659</v>
       </c>
       <c r="G2">
-        <v>-7.037687969327055</v>
+        <v>-7.247212396507528</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.76742528999799</v>
       </c>
       <c r="E3">
-        <v>-11.80284917676134</v>
+        <v>-9.671604397583422</v>
       </c>
       <c r="F3">
-        <v>-3.884428202446815</v>
+        <v>-4.139976572668039</v>
       </c>
       <c r="G3">
-        <v>-7.761273907845558</v>
+        <v>-7.264361022400953</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.68179174145396</v>
       </c>
       <c r="E4">
-        <v>-12.52074816119732</v>
+        <v>-11.42411931007784</v>
       </c>
       <c r="F4">
-        <v>-3.418821830719448</v>
+        <v>-3.248811000697023</v>
       </c>
       <c r="G4">
-        <v>-6.564584527400888</v>
+        <v>-5.558943419482019</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.5465889954575</v>
       </c>
       <c r="E5">
-        <v>-12.5078057824834</v>
+        <v>-12.60289467969646</v>
       </c>
       <c r="F5">
-        <v>-3.79175606709896</v>
+        <v>-3.921482169750351</v>
       </c>
       <c r="G5">
-        <v>-7.50034995062236</v>
+        <v>-6.452952931816664</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.30538354812073</v>
       </c>
       <c r="E6">
-        <v>-13.71906389615903</v>
+        <v>-12.54246672253811</v>
       </c>
       <c r="F6">
-        <v>-3.530571287524686</v>
+        <v>-3.533813133533591</v>
       </c>
       <c r="G6">
-        <v>-6.573029729071569</v>
+        <v>-6.493702436859553</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.93485028404319</v>
       </c>
       <c r="E7">
-        <v>-13.3218306846802</v>
+        <v>-12.6142566209817</v>
       </c>
       <c r="F7">
-        <v>-3.573996503726036</v>
+        <v>-3.995801529097136</v>
       </c>
       <c r="G7">
-        <v>-7.146886313939915</v>
+        <v>-5.646583491543145</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.41290771824233</v>
       </c>
       <c r="E8">
-        <v>-12.84339287729582</v>
+        <v>-13.92566646581098</v>
       </c>
       <c r="F8">
-        <v>-3.314766017251415</v>
+        <v>-3.995637615534888</v>
       </c>
       <c r="G8">
-        <v>-5.63597650363532</v>
+        <v>-5.851661856064378</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.74447565861499</v>
       </c>
       <c r="E9">
-        <v>-15.2203345422339</v>
+        <v>-15.51775565810967</v>
       </c>
       <c r="F9">
-        <v>-3.222791504359311</v>
+        <v>-4.250807480042322</v>
       </c>
       <c r="G9">
-        <v>-5.34131477682141</v>
+        <v>-5.507679621806404</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.96009408143035</v>
       </c>
       <c r="E10">
-        <v>-15.04567129975805</v>
+        <v>-15.35388829766811</v>
       </c>
       <c r="F10">
-        <v>-3.364730355177614</v>
+        <v>-3.487941091692887</v>
       </c>
       <c r="G10">
-        <v>-6.180134184470864</v>
+        <v>-5.652247834960838</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.10260879998444</v>
       </c>
       <c r="E11">
-        <v>-15.03575847015526</v>
+        <v>-16.1216231385585</v>
       </c>
       <c r="F11">
-        <v>-3.315900742539827</v>
+        <v>-3.327745279081399</v>
       </c>
       <c r="G11">
-        <v>-5.366176973821336</v>
+        <v>-5.911913784879113</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.250100467806044</v>
       </c>
       <c r="E12">
-        <v>-16.86245431536933</v>
+        <v>-17.75410179053161</v>
       </c>
       <c r="F12">
-        <v>-3.204606601185277</v>
+        <v>-2.652495044944777</v>
       </c>
       <c r="G12">
-        <v>-4.368411653740393</v>
+        <v>-4.000891440698203</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.457070766582808</v>
       </c>
       <c r="E13">
-        <v>-17.14716400470557</v>
+        <v>-16.68413206589528</v>
       </c>
       <c r="F13">
-        <v>-3.2906849769542</v>
+        <v>-3.319230484227038</v>
       </c>
       <c r="G13">
-        <v>-5.023181282134066</v>
+        <v>-4.992826890084489</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.807870482864216</v>
       </c>
       <c r="E14">
-        <v>-17.04357516178011</v>
+        <v>-16.83741185410691</v>
       </c>
       <c r="F14">
-        <v>-2.836349840227016</v>
+        <v>-3.26977293219378</v>
       </c>
       <c r="G14">
-        <v>-4.678593218042407</v>
+        <v>-4.497095869397404</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.330221479395603</v>
       </c>
       <c r="E15">
-        <v>-18.79637989661103</v>
+        <v>-17.39265710913539</v>
       </c>
       <c r="F15">
-        <v>-2.632598155676154</v>
+        <v>-2.771826493820182</v>
       </c>
       <c r="G15">
-        <v>-4.160211444775628</v>
+        <v>-5.044415121222952</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.064235351707563</v>
       </c>
       <c r="E16">
-        <v>-18.45402273315714</v>
+        <v>-17.47143444297282</v>
       </c>
       <c r="F16">
-        <v>-2.089284877648877</v>
+        <v>-2.607248566940672</v>
       </c>
       <c r="G16">
-        <v>-4.596038143929602</v>
+        <v>-3.953348696208729</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.994979543313984</v>
       </c>
       <c r="E17">
-        <v>-20.36493008101784</v>
+        <v>-20.06404015405219</v>
       </c>
       <c r="F17">
-        <v>-1.703601808650078</v>
+        <v>-2.204726744795963</v>
       </c>
       <c r="G17">
-        <v>-4.463470658355026</v>
+        <v>-3.68207266308423</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.112272123205782</v>
       </c>
       <c r="E18">
-        <v>-19.99170683872768</v>
+        <v>-21.76139825313319</v>
       </c>
       <c r="F18">
-        <v>-1.887466898020767</v>
+        <v>-1.164801300628846</v>
       </c>
       <c r="G18">
-        <v>-5.064162525364704</v>
+        <v>-3.60853220447486</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.375690103711636</v>
       </c>
       <c r="E19">
-        <v>-21.77715734267988</v>
+        <v>-21.41660477066318</v>
       </c>
       <c r="F19">
-        <v>-1.064567761387726</v>
+        <v>-1.588406999625801</v>
       </c>
       <c r="G19">
-        <v>-4.232404511350515</v>
+        <v>-2.910056753871729</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.746234541224178</v>
       </c>
       <c r="E20">
-        <v>-21.67648483701536</v>
+        <v>-22.35190220678539</v>
       </c>
       <c r="F20">
-        <v>-1.047423353000136</v>
+        <v>-1.062144691337104</v>
       </c>
       <c r="G20">
-        <v>-3.579022001537796</v>
+        <v>-4.894447408293967</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.183460780988332</v>
       </c>
       <c r="E21">
-        <v>-22.9441269805605</v>
+        <v>-24.39791657666494</v>
       </c>
       <c r="F21">
-        <v>-1.23551297790026</v>
+        <v>-0.7568172767817862</v>
       </c>
       <c r="G21">
-        <v>-4.867002985773409</v>
+        <v>-5.790708091595316</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-8.638034080218892</v>
       </c>
       <c r="E22">
-        <v>-22.88935055896372</v>
+        <v>-24.56896156840866</v>
       </c>
       <c r="F22">
-        <v>-0.09809697313756419</v>
+        <v>-1.371135217674832</v>
       </c>
       <c r="G22">
-        <v>-5.762197673411113</v>
+        <v>-4.360972857913651</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.080152152278675</v>
       </c>
       <c r="E23">
-        <v>-24.18602927784605</v>
+        <v>-24.24088268350096</v>
       </c>
       <c r="F23">
-        <v>0.1097588852931592</v>
+        <v>-0.6629573619973519</v>
       </c>
       <c r="G23">
-        <v>-4.826346176005619</v>
+        <v>-5.282198365126644</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.463569132217724</v>
       </c>
       <c r="E24">
-        <v>-23.85936327682874</v>
+        <v>-26.37163838748604</v>
       </c>
       <c r="F24">
-        <v>0.3039148957023737</v>
+        <v>0.1261605356064079</v>
       </c>
       <c r="G24">
-        <v>-4.278205908886332</v>
+        <v>-4.658587591348591</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.775126128195019</v>
       </c>
       <c r="E25">
-        <v>-24.76862651588085</v>
+        <v>-25.05862546285805</v>
       </c>
       <c r="F25">
-        <v>0.01730292580276203</v>
+        <v>0.05074921103092772</v>
       </c>
       <c r="G25">
-        <v>-5.025227199277336</v>
+        <v>-5.419787948284294</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.983250001092049</v>
       </c>
       <c r="E26">
-        <v>-24.38673577434</v>
+        <v>-25.25078672889954</v>
       </c>
       <c r="F26">
-        <v>0.52282660512878</v>
+        <v>0.5964158760485471</v>
       </c>
       <c r="G26">
-        <v>-4.619741649990783</v>
+        <v>-4.826995042931316</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.09010530410013</v>
       </c>
       <c r="E27">
-        <v>-24.08309253517769</v>
+        <v>-23.77650578791039</v>
       </c>
       <c r="F27">
-        <v>0.6021235521677908</v>
+        <v>0.4037002461694247</v>
       </c>
       <c r="G27">
-        <v>-4.859491357944803</v>
+        <v>-6.636648482699743</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.0845363122563</v>
       </c>
       <c r="E28">
-        <v>-25.35283589066239</v>
+        <v>-24.23052606344541</v>
       </c>
       <c r="F28">
-        <v>0.4873302125930779</v>
+        <v>0.9519847770652655</v>
       </c>
       <c r="G28">
-        <v>-5.069889769147643</v>
+        <v>-6.552461309636077</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.978053628151638</v>
       </c>
       <c r="E29">
-        <v>-23.53310936694612</v>
+        <v>-26.12374066335815</v>
       </c>
       <c r="F29">
-        <v>0.7207858852939223</v>
+        <v>0.7175804645210728</v>
       </c>
       <c r="G29">
-        <v>-4.725202388689806</v>
+        <v>-4.915277360827061</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.777354119073376</v>
       </c>
       <c r="E30">
-        <v>-24.45123482963125</v>
+        <v>-25.45005769913307</v>
       </c>
       <c r="F30">
-        <v>0.4874299860657506</v>
+        <v>0.6786735612964719</v>
       </c>
       <c r="G30">
-        <v>-5.455690814657689</v>
+        <v>-6.301978813043741</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.498611740632429</v>
       </c>
       <c r="E31">
-        <v>-24.14250611415833</v>
+        <v>-24.98838430252508</v>
       </c>
       <c r="F31">
-        <v>0.8074478566926843</v>
+        <v>0.0005813668945946254</v>
       </c>
       <c r="G31">
-        <v>-4.476928025972163</v>
+        <v>-5.568481101180659</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.160206752483433</v>
       </c>
       <c r="E32">
-        <v>-22.57285551056764</v>
+        <v>-25.14013346652211</v>
       </c>
       <c r="F32">
-        <v>0.2558288329918858</v>
+        <v>-0.09362379577940547</v>
       </c>
       <c r="G32">
-        <v>-5.265466867971168</v>
+        <v>-5.331025601285355</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.778663801148051</v>
       </c>
       <c r="E33">
-        <v>-22.57192717339607</v>
+        <v>-23.89743415781122</v>
       </c>
       <c r="F33">
-        <v>0.4572144609050814</v>
+        <v>-0.2887157763846447</v>
       </c>
       <c r="G33">
-        <v>-5.081668690176371</v>
+        <v>-5.733405858856071</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.382616432805408</v>
       </c>
       <c r="E34">
-        <v>-23.23970047904115</v>
+        <v>-24.6062399664398</v>
       </c>
       <c r="F34">
-        <v>0.1587991308176995</v>
+        <v>0.07287912564032084</v>
       </c>
       <c r="G34">
-        <v>-4.998646829142528</v>
+        <v>-4.371457355636522</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.982311800914523</v>
       </c>
       <c r="E35">
-        <v>-23.23958726719096</v>
+        <v>-23.85623410128944</v>
       </c>
       <c r="F35">
-        <v>-0.03944680011813741</v>
+        <v>0.03336803860897979</v>
       </c>
       <c r="G35">
-        <v>-3.921928308495506</v>
+        <v>-4.815186326992737</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.608664501178779</v>
       </c>
       <c r="E36">
-        <v>-21.78941139334464</v>
+        <v>-22.55209245724247</v>
       </c>
       <c r="F36">
-        <v>0.2972760005048516</v>
+        <v>0.03313919310419879</v>
       </c>
       <c r="G36">
-        <v>-4.09638412677848</v>
+        <v>-4.42820341672517</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.263248519183494</v>
       </c>
       <c r="E37">
-        <v>-20.32344925910758</v>
+        <v>-22.31641255598728</v>
       </c>
       <c r="F37">
-        <v>-0.3334317129070775</v>
+        <v>0.252364476301862</v>
       </c>
       <c r="G37">
-        <v>-4.080281633275464</v>
+        <v>-5.791413237795181</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.969606143913512</v>
       </c>
       <c r="E38">
-        <v>-20.58154057822674</v>
+        <v>-21.86669433075954</v>
       </c>
       <c r="F38">
-        <v>-0.3538219265683604</v>
+        <v>-0.5346415494636593</v>
       </c>
       <c r="G38">
-        <v>-4.300439532728078</v>
+        <v>-5.00849239157632</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.723498375396193</v>
       </c>
       <c r="E39">
-        <v>-19.96207250482148</v>
+        <v>-20.92857112685654</v>
       </c>
       <c r="F39">
-        <v>-0.4302262347528211</v>
+        <v>-0.2805945324502712</v>
       </c>
       <c r="G39">
-        <v>-4.555328365433184</v>
+        <v>-4.726566333451986</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.536901636267374</v>
       </c>
       <c r="E40">
-        <v>-19.85810779855338</v>
+        <v>-21.87347345634902</v>
       </c>
       <c r="F40">
-        <v>-0.2331118616935657</v>
+        <v>-0.518826662192081</v>
       </c>
       <c r="G40">
-        <v>-4.539490715573311</v>
+        <v>-4.673488356820851</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.40391777760116</v>
       </c>
       <c r="E41">
-        <v>-19.54498646329302</v>
+        <v>-21.44067361001395</v>
       </c>
       <c r="F41">
-        <v>-0.04797426461982111</v>
+        <v>-1.585882572396591</v>
       </c>
       <c r="G41">
-        <v>-3.654270701645431</v>
+        <v>-3.973178863988963</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.32458309706531</v>
       </c>
       <c r="E42">
-        <v>-20.09052719852306</v>
+        <v>-20.18785316189591</v>
       </c>
       <c r="F42">
-        <v>-0.3833588337442638</v>
+        <v>-0.6137144021156354</v>
       </c>
       <c r="G42">
-        <v>-4.053171575854373</v>
+        <v>-2.655081846982601</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.296076009597089</v>
       </c>
       <c r="E43">
-        <v>-19.09744190558897</v>
+        <v>-18.40230755998954</v>
       </c>
       <c r="F43">
-        <v>-0.2143750370080016</v>
+        <v>-0.7533584630624665</v>
       </c>
       <c r="G43">
-        <v>-4.039846630058807</v>
+        <v>-4.572116141862828</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.311363270081531</v>
       </c>
       <c r="E44">
-        <v>-19.40063229735051</v>
+        <v>-19.29576189628088</v>
       </c>
       <c r="F44">
-        <v>-0.6825097952293673</v>
+        <v>-0.5890378883942157</v>
       </c>
       <c r="G44">
-        <v>-4.18632171744386</v>
+        <v>-4.112638905376302</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.375289516304682</v>
       </c>
       <c r="E45">
-        <v>-17.00460764294411</v>
+        <v>-17.27714479414773</v>
       </c>
       <c r="F45">
-        <v>-0.5304399776699984</v>
+        <v>-0.236405178144722</v>
       </c>
       <c r="G45">
-        <v>-3.412379070727503</v>
+        <v>-4.222565570007801</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.47688569573801</v>
       </c>
       <c r="E46">
-        <v>-16.9705399329844</v>
+        <v>-16.89808434886168</v>
       </c>
       <c r="F46">
-        <v>-0.6840467818203013</v>
+        <v>-1.383000342393305</v>
       </c>
       <c r="G46">
-        <v>-3.591237914577707</v>
+        <v>-3.933064983689614</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.62643212576911</v>
       </c>
       <c r="E47">
-        <v>-16.52911787213872</v>
+        <v>-17.03151130702368</v>
       </c>
       <c r="F47">
-        <v>-0.4629289700536879</v>
+        <v>-0.9143841375736455</v>
       </c>
       <c r="G47">
-        <v>-3.285677871848516</v>
+        <v>-2.978512214532778</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.809046621182322</v>
       </c>
       <c r="E48">
-        <v>-16.41279043182968</v>
+        <v>-19.56900096095569</v>
       </c>
       <c r="F48">
-        <v>-0.1645215584958832</v>
+        <v>-0.9900646921547502</v>
       </c>
       <c r="G48">
-        <v>-2.801249053632502</v>
+        <v>-4.422016007112272</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.036471085499373</v>
       </c>
       <c r="E49">
-        <v>-15.17271310956923</v>
+        <v>-16.02997135311726</v>
       </c>
       <c r="F49">
-        <v>-0.2835845692186209</v>
+        <v>-0.5077304266955545</v>
       </c>
       <c r="G49">
-        <v>-3.697539531843705</v>
+        <v>-2.478139808999634</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.293563597901525</v>
       </c>
       <c r="E50">
-        <v>-16.01438434558286</v>
+        <v>-15.98145328259908</v>
       </c>
       <c r="F50">
-        <v>-0.5787358814142821</v>
+        <v>-1.29538102076866</v>
       </c>
       <c r="G50">
-        <v>-2.959728179142953</v>
+        <v>-4.066337615464055</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.587022638620002</v>
       </c>
       <c r="E51">
-        <v>-14.61517191821887</v>
+        <v>-16.8338660589589</v>
       </c>
       <c r="F51">
-        <v>-0.4694649243667065</v>
+        <v>-0.943810185335468</v>
       </c>
       <c r="G51">
-        <v>-3.657144255173518</v>
+        <v>-3.697076055468207</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.906863002847818</v>
       </c>
       <c r="E52">
-        <v>-15.27816315531185</v>
+        <v>-15.73447031022074</v>
       </c>
       <c r="F52">
-        <v>-0.4968147336733881</v>
+        <v>-0.690280248303471</v>
       </c>
       <c r="G52">
-        <v>-3.270399704184779</v>
+        <v>-4.506905015830264</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.25287309125221</v>
       </c>
       <c r="E53">
-        <v>-15.53098785916008</v>
+        <v>-14.89266321998688</v>
       </c>
       <c r="F53">
-        <v>-0.8376345814996189</v>
+        <v>-0.8857372731222189</v>
       </c>
       <c r="G53">
-        <v>-3.330734396637997</v>
+        <v>-2.94043763028562</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.620925967162401</v>
       </c>
       <c r="E54">
-        <v>-14.82305151754097</v>
+        <v>-14.50474507954183</v>
       </c>
       <c r="F54">
-        <v>-0.6544140604365138</v>
+        <v>-0.7376710641170809</v>
       </c>
       <c r="G54">
-        <v>-3.215560517326752</v>
+        <v>-3.100671344931885</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.002261143004738</v>
       </c>
       <c r="E55">
-        <v>-14.16548086383518</v>
+        <v>-13.08981431889721</v>
       </c>
       <c r="F55">
-        <v>-0.2829265394107558</v>
+        <v>-0.6877597803390491</v>
       </c>
       <c r="G55">
-        <v>-2.895735333868841</v>
+        <v>-3.490590709092785</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.398075043827191</v>
       </c>
       <c r="E56">
-        <v>-13.1749451017674</v>
+        <v>-16.19028838993681</v>
       </c>
       <c r="F56">
-        <v>-0.4713701225829802</v>
+        <v>-0.7354134913346221</v>
       </c>
       <c r="G56">
-        <v>-3.324384770293674</v>
+        <v>-4.140176023171959</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.791460831336192</v>
       </c>
       <c r="E57">
-        <v>-13.78844464643055</v>
+        <v>-14.00539930766403</v>
       </c>
       <c r="F57">
-        <v>-0.4150495809651648</v>
+        <v>-0.6420714483845364</v>
       </c>
       <c r="G57">
-        <v>-3.629623690105556</v>
+        <v>-4.476140116133817</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-10.18792971670091</v>
       </c>
       <c r="E58">
-        <v>-14.13026744995153</v>
+        <v>-12.7781466237933</v>
       </c>
       <c r="F58">
-        <v>-1.238114214866369</v>
+        <v>-1.17773542684024</v>
       </c>
       <c r="G58">
-        <v>-3.655717410046092</v>
+        <v>-5.672372641294068</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-10.5643210217074</v>
       </c>
       <c r="E59">
-        <v>-14.49743159401944</v>
+        <v>-12.78025689268088</v>
       </c>
       <c r="F59">
-        <v>-0.4212173236528438</v>
+        <v>-0.940942885775565</v>
       </c>
       <c r="G59">
-        <v>-3.923441227806953</v>
+        <v>-3.864238741928166</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.92861337560078</v>
       </c>
       <c r="E60">
-        <v>-13.79882843733014</v>
+        <v>-12.77701450529139</v>
       </c>
       <c r="F60">
-        <v>-0.7917839196887737</v>
+        <v>-0.7877953563407395</v>
       </c>
       <c r="G60">
-        <v>-4.085350078496089</v>
+        <v>-4.800831801534456</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.25933895570282</v>
       </c>
       <c r="E61">
-        <v>-13.27599799924857</v>
+        <v>-12.25416142483977</v>
       </c>
       <c r="F61">
-        <v>-0.6266904965337885</v>
+        <v>-0.7502219334969387</v>
       </c>
       <c r="G61">
-        <v>-4.120024732474415</v>
+        <v>-5.452790776765288</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.56336662413422</v>
       </c>
       <c r="E62">
-        <v>-13.12640891735319</v>
+        <v>-13.13849541447966</v>
       </c>
       <c r="F62">
-        <v>-0.6622328165410384</v>
+        <v>-0.4124934796176455</v>
       </c>
       <c r="G62">
-        <v>-3.944519471255493</v>
+        <v>-4.022631793254596</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.82814113600793</v>
       </c>
       <c r="E63">
-        <v>-13.37189296483499</v>
+        <v>-13.31302280273528</v>
       </c>
       <c r="F63">
-        <v>-0.5518667268529365</v>
+        <v>-1.034771126441691</v>
       </c>
       <c r="G63">
-        <v>-4.298956408326483</v>
+        <v>-3.319650690172517</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-12.05605935514285</v>
       </c>
       <c r="E64">
-        <v>-12.28215192268118</v>
+        <v>-13.13594588361335</v>
       </c>
       <c r="F64">
-        <v>-1.126702879274077</v>
+        <v>-1.033734590920035</v>
       </c>
       <c r="G64">
-        <v>-5.290554182067765</v>
+        <v>-4.978654444630869</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-12.24549815733511</v>
       </c>
       <c r="E65">
-        <v>-12.90363969549386</v>
+        <v>-13.66277496424369</v>
       </c>
       <c r="F65">
-        <v>-0.5694308173081176</v>
+        <v>-1.069960280029797</v>
       </c>
       <c r="G65">
-        <v>-5.362763801370348</v>
+        <v>-6.098353778014248</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-12.39373610749398</v>
       </c>
       <c r="E66">
-        <v>-11.06964847865344</v>
+        <v>-11.86914603623363</v>
       </c>
       <c r="F66">
-        <v>-0.9289922409376589</v>
+        <v>-1.604271773633716</v>
       </c>
       <c r="G66">
-        <v>-5.035334294808731</v>
+        <v>-5.412710001921332</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-12.50958123324402</v>
       </c>
       <c r="E67">
-        <v>-13.55713019411875</v>
+        <v>-12.77351399488346</v>
       </c>
       <c r="F67">
-        <v>-1.174002631997549</v>
+        <v>-1.35582870000211</v>
       </c>
       <c r="G67">
-        <v>-5.284946117924239</v>
+        <v>-6.61299794536719</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-12.5840993239852</v>
       </c>
       <c r="E68">
-        <v>-12.69576009617176</v>
+        <v>-12.81953687622341</v>
       </c>
       <c r="F68">
-        <v>-0.5502853964963701</v>
+        <v>-1.088248124088334</v>
       </c>
       <c r="G68">
-        <v>-5.57937941709594</v>
+        <v>-4.312566061038427</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-12.6349617815693</v>
       </c>
       <c r="E69">
-        <v>-12.65329659540183</v>
+        <v>-11.7394188413359</v>
       </c>
       <c r="F69">
-        <v>-1.127819391944462</v>
+        <v>-1.264090159291407</v>
       </c>
       <c r="G69">
-        <v>-5.156199001901983</v>
+        <v>-5.910847789215468</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-12.64794852720324</v>
       </c>
       <c r="E70">
-        <v>-12.32813857622908</v>
+        <v>-11.7949152902999</v>
       </c>
       <c r="F70">
-        <v>-1.145741399936532</v>
+        <v>-0.872933010795891</v>
       </c>
       <c r="G70">
-        <v>-6.243498026092515</v>
+        <v>-4.772162477164368</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.64355847680596</v>
       </c>
       <c r="E71">
-        <v>-10.99499658463699</v>
+        <v>-15.06328253517388</v>
       </c>
       <c r="F71">
-        <v>-1.115552797776426</v>
+        <v>-0.9109934232086896</v>
       </c>
       <c r="G71">
-        <v>-5.110447262549255</v>
+        <v>-6.29557290742525</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.60613624660232</v>
       </c>
       <c r="E72">
-        <v>-13.23699878109451</v>
+        <v>-12.88050372178868</v>
       </c>
       <c r="F72">
-        <v>-1.375180002582865</v>
+        <v>-1.891909984966532</v>
       </c>
       <c r="G72">
-        <v>-5.545711168961552</v>
+        <v>-6.194293387742327</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.5512099871388</v>
       </c>
       <c r="E73">
-        <v>-12.53303843965414</v>
+        <v>-12.88138677422017</v>
       </c>
       <c r="F73">
-        <v>-1.243940668929271</v>
+        <v>-1.704620131553706</v>
       </c>
       <c r="G73">
-        <v>-5.884687858364146</v>
+        <v>-6.568868373328705</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.46876249216777</v>
       </c>
       <c r="E74">
-        <v>-12.54934547455576</v>
+        <v>-13.37734071906622</v>
       </c>
       <c r="F74">
-        <v>-1.578162797911781</v>
+        <v>-1.443628564101115</v>
       </c>
       <c r="G74">
-        <v>-5.129751053588745</v>
+        <v>-7.011723360662551</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.36641769942673</v>
       </c>
       <c r="E75">
-        <v>-13.02826330018495</v>
+        <v>-14.18471329294575</v>
       </c>
       <c r="F75">
-        <v>-1.492164399291588</v>
+        <v>-1.514402005903231</v>
       </c>
       <c r="G75">
-        <v>-5.125662529847745</v>
+        <v>-5.698635199057106</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-12.24463856328345</v>
       </c>
       <c r="E76">
-        <v>-12.21389423396357</v>
+        <v>-14.13442458909057</v>
       </c>
       <c r="F76">
-        <v>-1.366034100921202</v>
+        <v>-2.303175447470383</v>
       </c>
       <c r="G76">
-        <v>-5.265801233070634</v>
+        <v>-4.754431195256031</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-12.10479365810118</v>
       </c>
       <c r="E77">
-        <v>-13.53717773764095</v>
+        <v>-14.2203976681262</v>
       </c>
       <c r="F77">
-        <v>-1.877391360986741</v>
+        <v>-1.429674531280178</v>
       </c>
       <c r="G77">
-        <v>-4.980289854127268</v>
+        <v>-5.880433807346183</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-11.95898576441493</v>
       </c>
       <c r="E78">
-        <v>-14.19392420907736</v>
+        <v>-17.22262196709538</v>
       </c>
       <c r="F78">
-        <v>-1.424483143289368</v>
+        <v>-1.987226117340213</v>
       </c>
       <c r="G78">
-        <v>-5.692815259999067</v>
+        <v>-6.299320444975706</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.80212830436283</v>
       </c>
       <c r="E79">
-        <v>-14.78613539743045</v>
+        <v>-14.71905058348082</v>
       </c>
       <c r="F79">
-        <v>-1.775337351795823</v>
+        <v>-1.903736308890076</v>
       </c>
       <c r="G79">
-        <v>-4.879374494453665</v>
+        <v>-4.584421439632298</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.65702926963871</v>
       </c>
       <c r="E80">
-        <v>-15.49605521066491</v>
+        <v>-16.03925472483299</v>
       </c>
       <c r="F80">
-        <v>-1.676758785236337</v>
+        <v>-1.621322743372295</v>
       </c>
       <c r="G80">
-        <v>-3.835986546296026</v>
+        <v>-4.593300322768624</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-11.51275201414623</v>
       </c>
       <c r="E81">
-        <v>-15.84745120823811</v>
+        <v>-17.61920307831711</v>
       </c>
       <c r="F81">
-        <v>-1.457804315750214</v>
+        <v>-2.319558885165604</v>
       </c>
       <c r="G81">
-        <v>-3.913605597009778</v>
+        <v>-5.998375302728259</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-11.39720704857653</v>
       </c>
       <c r="E82">
-        <v>-16.65094287989307</v>
+        <v>-16.69109233044507</v>
       </c>
       <c r="F82">
-        <v>-1.533344712357802</v>
+        <v>-1.768091897232688</v>
       </c>
       <c r="G82">
-        <v>-5.108815163598394</v>
+        <v>-5.945899845385271</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-11.29791206532432</v>
       </c>
       <c r="E83">
-        <v>-17.69597429816915</v>
+        <v>-17.65287681103815</v>
       </c>
       <c r="F83">
-        <v>-1.552764906145879</v>
+        <v>-2.566696985122888</v>
       </c>
       <c r="G83">
-        <v>-4.222125267451078</v>
+        <v>-3.363230711651483</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-11.23950713322372</v>
       </c>
       <c r="E84">
-        <v>-17.3351002044979</v>
+        <v>-16.88630578796773</v>
       </c>
       <c r="F84">
-        <v>-2.064298749420989</v>
+        <v>-2.788772938968342</v>
       </c>
       <c r="G84">
-        <v>-4.304339355373338</v>
+        <v>-5.487419083106065</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-11.21574077058321</v>
       </c>
       <c r="E85">
-        <v>-18.4699991894562</v>
+        <v>-17.55462251049373</v>
       </c>
       <c r="F85">
-        <v>-2.220247062767269</v>
+        <v>-2.918712841918317</v>
       </c>
       <c r="G85">
-        <v>-4.120296197208636</v>
+        <v>-3.971907614501883</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-11.24117445615517</v>
       </c>
       <c r="E86">
-        <v>-19.60804546384983</v>
+        <v>-20.39834116224644</v>
       </c>
       <c r="F86">
-        <v>-1.804548015553146</v>
+        <v>-3.521880701313712</v>
       </c>
       <c r="G86">
-        <v>-4.48856790408824</v>
+        <v>-4.674216676839491</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-11.31842556283145</v>
       </c>
       <c r="E87">
-        <v>-21.5992245419705</v>
+        <v>-22.74004224245682</v>
       </c>
       <c r="F87">
-        <v>-2.603135682678276</v>
+        <v>-2.001880148175774</v>
       </c>
       <c r="G87">
-        <v>-3.602394453045051</v>
+        <v>-3.924748893294965</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-11.45143427007038</v>
       </c>
       <c r="E88">
-        <v>-21.56705879109402</v>
+        <v>-22.0079510204808</v>
       </c>
       <c r="F88">
-        <v>-2.733508729196124</v>
+        <v>-3.270381867118266</v>
       </c>
       <c r="G88">
-        <v>-3.151743130966222</v>
+        <v>-5.834506609079874</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-11.65281846859677</v>
       </c>
       <c r="E89">
-        <v>-24.26179517646838</v>
+        <v>-24.151169084935</v>
       </c>
       <c r="F89">
-        <v>-2.466751680358377</v>
+        <v>-1.885969504077719</v>
       </c>
       <c r="G89">
-        <v>-3.760721293460696</v>
+        <v>-3.810488724552559</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-11.91519800738413</v>
       </c>
       <c r="E90">
-        <v>-25.2808739102065</v>
+        <v>-23.04410210122784</v>
       </c>
       <c r="F90">
-        <v>-2.865446477158427</v>
+        <v>-2.770159643344182</v>
       </c>
       <c r="G90">
-        <v>-3.1355810476435</v>
+        <v>-3.103541587914433</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-12.25762573552827</v>
       </c>
       <c r="E91">
-        <v>-26.34979302887304</v>
+        <v>-28.64807510029789</v>
       </c>
       <c r="F91">
-        <v>-2.734960987520582</v>
+        <v>-3.261733249114052</v>
       </c>
       <c r="G91">
-        <v>-2.956321627783043</v>
+        <v>-4.526877537068687</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-12.65748851884944</v>
       </c>
       <c r="E92">
-        <v>-28.5450613735714</v>
+        <v>-27.9775801817742</v>
       </c>
       <c r="F92">
-        <v>-3.026774639499455</v>
+        <v>-3.649131471619272</v>
       </c>
       <c r="G92">
-        <v>-3.597792794745464</v>
+        <v>-2.782229969509389</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-13.1291944498324</v>
       </c>
       <c r="E93">
-        <v>-30.70831340703553</v>
+        <v>-28.21225023332568</v>
       </c>
       <c r="F93">
-        <v>-2.760765099853795</v>
+        <v>-3.847065412489767</v>
       </c>
       <c r="G93">
-        <v>-3.379174298968613</v>
+        <v>-4.3457609011607</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-13.63414761129055</v>
       </c>
       <c r="E94">
-        <v>-32.90967934198522</v>
+        <v>-32.65639952649921</v>
       </c>
       <c r="F94">
-        <v>-3.751158557809627</v>
+        <v>-3.43766713926022</v>
       </c>
       <c r="G94">
-        <v>-3.552726338319365</v>
+        <v>-4.855968937491018</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-14.17097719863996</v>
       </c>
       <c r="E95">
-        <v>-34.05337035922941</v>
+        <v>-33.64851799023267</v>
       </c>
       <c r="F95">
-        <v>-3.39493637810279</v>
+        <v>-4.340182339674232</v>
       </c>
       <c r="G95">
-        <v>-3.604145731635326</v>
+        <v>-4.87235613791041</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-14.69588075126155</v>
       </c>
       <c r="E96">
-        <v>-36.78512701961647</v>
+        <v>-34.76618386735478</v>
       </c>
       <c r="F96">
-        <v>-3.630204602223855</v>
+        <v>-3.86003121281947</v>
       </c>
       <c r="G96">
-        <v>-4.260312410246571</v>
+        <v>-5.596624048810003</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-15.19072236580667</v>
       </c>
       <c r="E97">
-        <v>-39.10425818537264</v>
+        <v>-38.6712477649962</v>
       </c>
       <c r="F97">
-        <v>-3.634622349874973</v>
+        <v>-4.532922516995044</v>
       </c>
       <c r="G97">
-        <v>-5.116661156526467</v>
+        <v>-5.047440959845845</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-15.61838903450437</v>
       </c>
       <c r="E98">
-        <v>-40.68785196043294</v>
+        <v>-39.32452089686872</v>
       </c>
       <c r="F98">
-        <v>-3.87409531320153</v>
+        <v>-4.542766041112458</v>
       </c>
       <c r="G98">
-        <v>-4.354547089021925</v>
+        <v>-4.984000975676792</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-15.95847097257038</v>
       </c>
       <c r="E99">
-        <v>-42.1699354621373</v>
+        <v>-42.40785242955229</v>
       </c>
       <c r="F99">
-        <v>-4.241724926617278</v>
+        <v>-4.255837330029759</v>
       </c>
       <c r="G99">
-        <v>-5.124229063629241</v>
+        <v>-6.479367774674508</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-16.19098363756484</v>
       </c>
       <c r="E100">
-        <v>-44.67755982998873</v>
+        <v>-44.40514268334631</v>
       </c>
       <c r="F100">
-        <v>-3.894680322690412</v>
+        <v>-4.678644841245331</v>
       </c>
       <c r="G100">
-        <v>-5.312767942636274</v>
+        <v>-6.52083235755388</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-16.30776684506366</v>
       </c>
       <c r="E101">
-        <v>-46.66045180067536</v>
+        <v>-44.69452575785846</v>
       </c>
       <c r="F101">
-        <v>-4.641544946470247</v>
+        <v>-5.019591385544798</v>
       </c>
       <c r="G101">
-        <v>-6.144568993742474</v>
+        <v>-7.059276036788642</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-16.30047556082495</v>
       </c>
       <c r="E102">
-        <v>-49.38250507338249</v>
+        <v>-49.67713778138804</v>
       </c>
       <c r="F102">
-        <v>-4.582904275686313</v>
+        <v>-5.477049590337228</v>
       </c>
       <c r="G102">
-        <v>-7.340440669438944</v>
+        <v>-8.133958571929012</v>
       </c>
     </row>
   </sheetData>
